--- a/AAII_Financials/Yearly/RNA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RNA_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>RNA</t>
   </si>
@@ -656,49 +656,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -711,30 +711,33 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E8" s="3">
         <v>9200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -747,9 +750,12 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -783,9 +789,12 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -819,9 +828,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,29 +848,30 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E12" s="3">
         <v>150400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>101200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>37600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8400</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,9 +884,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,9 +923,12 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -943,9 +962,12 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -979,9 +1001,12 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,29 +1018,30 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>245200</v>
+      </c>
+      <c r="E17" s="3">
         <v>188100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>127400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10900</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1028,30 +1054,33 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-235600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-178900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-118100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-44300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-17300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10500</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1064,9 +1093,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,28 +1113,29 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1116,30 +1149,33 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-210100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-172600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-117400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-43800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10100</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,30 +1188,33 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,30 +1227,33 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-212200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-174000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-118000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-44400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11200</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,9 +1266,12 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1260,9 +1305,12 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,30 +1344,33 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-212200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-174000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-118000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-44400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11200</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1332,30 +1383,33 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-212200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-174000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-118000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-44400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11200</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1368,9 +1422,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,29 +1578,32 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1548,30 +1617,33 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-212200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-174000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-118000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-44400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11200</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,9 +1656,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,30 +1695,33 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-212200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-174000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-118000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-44400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11200</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,35 +1734,38 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1697,9 +1778,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,29 +1815,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>185100</v>
+      </c>
+      <c r="E41" s="3">
         <v>340400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>320400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>321500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>94600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3100</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,24 +1851,27 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>410300</v>
+      </c>
+      <c r="E42" s="3">
         <v>270300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>85100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6700</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1798,35 +1887,38 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1837,9 +1929,12 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1873,30 +1968,33 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E45" s="3">
         <v>12200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1909,30 +2007,33 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>611300</v>
+      </c>
+      <c r="E46" s="3">
         <v>622900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>411100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>331700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>95700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3200</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,9 +2046,12 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1981,30 +2085,33 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E48" s="3">
         <v>15000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,9 +2124,12 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2053,9 +2163,12 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,29 +2241,32 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E52" s="3">
         <v>800</v>
       </c>
       <c r="F52" s="3">
+        <v>800</v>
+      </c>
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>600</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2161,9 +2280,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,30 +2319,33 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>628600</v>
+      </c>
+      <c r="E54" s="3">
         <v>638800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>427600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>333900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>96900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2233,9 +2358,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,29 +2395,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E57" s="3">
         <v>32600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2301,9 +2431,12 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2316,15 +2449,15 @@
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
         <v>2800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2700</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2337,30 +2470,33 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E59" s="3">
         <v>19300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,30 +2509,33 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E60" s="3">
         <v>51900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4600</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,9 +2548,12 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2425,14 +2567,14 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>1800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7600</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2445,30 +2587,33 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E62" s="3">
         <v>8800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2481,9 +2626,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,30 +2743,33 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E66" s="3">
         <v>60700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>46100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12400</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2625,9 +2782,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2729,14 +2896,14 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>134700</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>32700</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,30 +2955,33 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-570800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-358500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-184500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-66500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-22200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-41600</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2821,9 +2994,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,30 +3111,33 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>500800</v>
+      </c>
+      <c r="E76" s="3">
         <v>578100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>381400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>306200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-65300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-41100</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,9 +3150,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,35 +3189,38 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3042,30 +3233,33 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-212200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-174000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-118000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-44400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11200</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3078,9 +3272,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,29 +3292,30 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3130,9 +3328,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,30 +3523,33 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-119100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-136300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-94800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9700</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3346,9 +3562,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,28 +3582,29 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -3398,9 +3618,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,29 +3696,32 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-130100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-190000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-82500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -3506,9 +3735,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,8 +3755,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,30 +3908,33 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E100" s="3">
         <v>346200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>176300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>272000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>89200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3702,9 +3947,12 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3738,30 +3986,33 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-155300</v>
+      </c>
+      <c r="E102" s="3">
         <v>19900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>227100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>91500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4600</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3774,7 +4025,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RNA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RNA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>RNA</t>
   </si>
@@ -759,23 +759,23 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>150400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>101200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>37600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>14500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>8400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -798,23 +798,23 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-181400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-141200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-91900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-8100</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -932,26 +932,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -972,22 +972,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>23400</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
-        <v>4900</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
@@ -1134,8 +1134,8 @@
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1159,16 +1159,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-210100</v>
+        <v>-234100</v>
       </c>
       <c r="E21" s="3">
-        <v>-172600</v>
+        <v>-177600</v>
       </c>
       <c r="F21" s="3">
-        <v>-117400</v>
+        <v>-117500</v>
       </c>
       <c r="G21" s="3">
-        <v>-43800</v>
+        <v>-44000</v>
       </c>
       <c r="H21" s="3">
         <v>-17000</v>
@@ -1176,8 +1176,8 @@
       <c r="I21" s="3">
         <v>-10100</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1200,11 +1200,11 @@
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
@@ -1275,26 +1275,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-23400</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
-        <v>-4900</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
@@ -1602,8 +1602,8 @@
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1872,14 +1872,14 @@
       <c r="G42" s="3">
         <v>6700</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1900,19 +1900,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+        <v>8600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F43" s="3">
+        <v>900</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H43" s="3">
+        <v>800</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1938,26 +1938,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1977,23 +1977,23 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>14900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>12200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2055,26 +2055,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2151,8 +2151,8 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2257,7 +2257,7 @@
         <v>800</v>
       </c>
       <c r="F52" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
@@ -2405,16 +2405,16 @@
         <v>8800</v>
       </c>
       <c r="E57" s="3">
-        <v>32600</v>
+        <v>4600</v>
       </c>
       <c r="F57" s="3">
-        <v>14100</v>
+        <v>2800</v>
       </c>
       <c r="G57" s="3">
         <v>7700</v>
       </c>
       <c r="H57" s="3">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="I57" s="3">
         <v>1600</v>
@@ -2440,17 +2440,17 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>2800</v>
@@ -2480,22 +2480,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>71900</v>
+        <v>28400</v>
       </c>
       <c r="E59" s="3">
-        <v>19300</v>
+        <v>5000</v>
       </c>
       <c r="F59" s="3">
-        <v>15600</v>
+        <v>4900</v>
       </c>
       <c r="G59" s="3">
-        <v>6800</v>
+        <v>3700</v>
       </c>
       <c r="H59" s="3">
-        <v>5500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>300</v>
+        <v>3800</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2558,19 +2558,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H61" s="3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="I61" s="3">
         <v>7600</v>
@@ -2596,20 +2596,20 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>47100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>8800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>16500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>13100</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>15500</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
@@ -2759,7 +2759,7 @@
         <v>60700</v>
       </c>
       <c r="F66" s="3">
-        <v>46100</v>
+        <v>46200</v>
       </c>
       <c r="G66" s="3">
         <v>27700</v>
@@ -3133,7 +3133,7 @@
         <v>306200</v>
       </c>
       <c r="H76" s="3">
-        <v>-65300</v>
+        <v>-65400</v>
       </c>
       <c r="I76" s="3">
         <v>-41100</v>
@@ -3956,26 +3956,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4013,8 +4013,8 @@
       <c r="I102" s="3">
         <v>-4600</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/RNA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RNA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>RNA</t>
   </si>
@@ -656,52 +656,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -714,33 +714,36 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E8" s="3">
         <v>9600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,33 +756,36 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>303600</v>
+      </c>
+      <c r="E9" s="3">
         <v>191000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>150400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>101200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>37600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8400</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -792,33 +798,36 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-292700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-181400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-141200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-91900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-30800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-12200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-8100</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,9 +840,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,32 +861,33 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>303600</v>
+      </c>
+      <c r="E12" s="3">
         <v>191000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>150400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>101200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>37600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8400</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,9 +942,12 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -953,8 +972,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -965,33 +984,36 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E15" s="3">
         <v>2100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>400</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1004,9 +1026,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,32 +1044,33 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>389800</v>
+      </c>
+      <c r="E17" s="3">
         <v>245200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>188100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>127400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10900</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1057,33 +1083,36 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-378900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-235600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-178900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-118100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-44300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-17300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10500</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1096,9 +1125,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,16 +1146,17 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1132,10 +1165,10 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1152,35 +1185,38 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-376400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-234100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-177600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-117500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-44000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10100</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
@@ -1191,9 +1227,12 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1206,18 +1245,18 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,33 +1269,36 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-322300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-212200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-174000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-118000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-44400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11200</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,9 +1311,12 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1296,8 +1341,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,33 +1395,36 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-322300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-212200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-174000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-118000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-44400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11200</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,33 +1437,36 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-322300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-212200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-174000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-118000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-44400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11200</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,9 +1479,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,17 +1647,20 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
@@ -1600,10 +1669,10 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1620,33 +1689,36 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-322300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-212200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-174000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-118000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-44400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11200</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,9 +1731,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,33 +1773,36 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-322300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-212200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-174000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-118000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-44400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11200</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,38 +1815,41 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1781,9 +1862,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,32 +1901,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>219900</v>
+      </c>
+      <c r="E41" s="3">
         <v>185100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>340400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>320400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>321500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>94600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1854,35 +1940,38 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1281600</v>
+      </c>
+      <c r="E42" s="3">
         <v>410300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>270300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>85100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6700</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -1890,38 +1979,41 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E43" s="3">
         <v>8600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1932,9 +2024,12 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1959,8 +2054,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1971,9 +2066,12 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2010,33 +2108,36 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1542300</v>
+      </c>
+      <c r="E46" s="3">
         <v>611300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>622900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>411100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>331700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>95700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2049,9 +2150,12 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2076,8 +2180,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2088,33 +2192,36 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E48" s="3">
         <v>16700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>700</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2127,9 +2234,12 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2151,11 +2261,11 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2166,9 +2276,12 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,32 +2360,35 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>600</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2283,9 +2402,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,33 +2444,36 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1563900</v>
+      </c>
+      <c r="E54" s="3">
         <v>628600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>638800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>427600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>333900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>96900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,9 +2486,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,32 +2525,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E57" s="3">
         <v>8800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,33 +2564,36 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1800</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>2800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,30 +2606,33 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E59" s="3">
         <v>28400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3800</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2512,33 +2648,36 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E60" s="3">
         <v>80700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>51900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2551,33 +2690,36 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7600</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2590,9 +2732,12 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2608,15 +2753,15 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,33 +2900,36 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>138900</v>
+      </c>
+      <c r="E66" s="3">
         <v>127800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12400</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2785,9 +2942,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2899,14 +3066,14 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>134700</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>32700</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,33 +3128,36 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-893100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-570800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-358500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-184500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-66500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-22200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-41600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,9 +3170,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,33 +3296,36 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1425000</v>
+      </c>
+      <c r="E76" s="3">
         <v>500800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>578100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>381400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>306200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-65400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-41100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3153,9 +3338,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,38 +3380,41 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3236,33 +3427,36 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-322300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-212200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-174000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-118000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-44400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11200</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3469,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,32 +3490,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,9 +3529,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,33 +3739,36 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-119100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-136300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-94800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-37100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9700</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3565,9 +3781,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,31 +3802,32 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3621,9 +3841,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,32 +3925,35 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-854200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-130100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-190000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-82500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3738,9 +3967,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,33 +4153,36 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1192400</v>
+      </c>
+      <c r="E100" s="3">
         <v>93900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>346200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>176300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>272000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>89200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3950,9 +4195,12 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3977,8 +4225,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3989,35 +4237,38 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-155300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>227100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>91500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4600</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -4028,7 +4279,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RNA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RNA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="92">
   <si>
     <t>RNA</t>
   </si>
@@ -656,55 +656,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
-        <v>44926</v>
-      </c>
-      <c r="G7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44196</v>
-      </c>
-      <c r="I7" s="2">
-        <v>43830</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="G7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,36 +719,39 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E8" s="3">
         <v>10900</v>
       </c>
-      <c r="E8" s="3">
-        <v>9600</v>
-      </c>
       <c r="F8" s="3">
-        <v>9200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>9300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>6800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J8" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,36 +764,39 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>303600</v>
+        <v>44300</v>
       </c>
       <c r="E9" s="3">
-        <v>191000</v>
+        <v>19200</v>
       </c>
       <c r="F9" s="3">
-        <v>150400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>101200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>37600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>14500</v>
-      </c>
-      <c r="J9" s="3">
+        <v>12700</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>8400</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,36 +809,39 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-292700</v>
+        <v>-25600</v>
       </c>
       <c r="E10" s="3">
-        <v>-181400</v>
+        <v>-8300</v>
       </c>
       <c r="F10" s="3">
-        <v>-141200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-91900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-30800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="J10" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>-8100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +854,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,35 +876,36 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>303600</v>
+        <v>44300</v>
       </c>
       <c r="E12" s="3">
-        <v>191000</v>
+        <v>19200</v>
       </c>
       <c r="F12" s="3">
-        <v>150400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>101200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>37600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>14500</v>
-      </c>
-      <c r="J12" s="3">
+        <v>12700</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>8400</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +918,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,9 +963,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -975,8 +996,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -987,36 +1008,39 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2800</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>2100</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>400</v>
       </c>
-      <c r="I15" s="3">
-        <v>300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1029,9 +1053,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,35 +1072,36 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>389800</v>
+        <v>68200</v>
       </c>
       <c r="E17" s="3">
-        <v>245200</v>
+        <v>24100</v>
       </c>
       <c r="F17" s="3">
-        <v>188100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>127400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>51100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>19700</v>
-      </c>
-      <c r="J17" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
         <v>10900</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,36 +1114,39 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-378900</v>
+        <v>-49600</v>
       </c>
       <c r="E18" s="3">
-        <v>-235600</v>
+        <v>-13200</v>
       </c>
       <c r="F18" s="3">
-        <v>-178900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-118100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-44300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="J18" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-10500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1159,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,28 +1181,29 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1188,38 +1223,41 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-376400</v>
+        <v>-49300</v>
       </c>
       <c r="E21" s="3">
-        <v>-234100</v>
+        <v>-13000</v>
       </c>
       <c r="F21" s="3">
-        <v>-177600</v>
+        <v>-6200</v>
       </c>
       <c r="G21" s="3">
-        <v>-117500</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>-44000</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>-17000</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-10100</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
@@ -1230,9 +1268,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1248,18 +1289,18 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,36 +1313,39 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-322300</v>
+        <v>-49600</v>
       </c>
       <c r="E23" s="3">
-        <v>-212200</v>
+        <v>-13200</v>
       </c>
       <c r="F23" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-118000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-44400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="J23" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
         <v>-11200</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,17 +1358,20 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>11900</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1344,8 +1391,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1356,9 +1403,12 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,36 +1448,39 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-322300</v>
+        <v>-49500</v>
       </c>
       <c r="E26" s="3">
-        <v>-212200</v>
+        <v>-25100</v>
       </c>
       <c r="F26" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-118000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-44400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="J26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
         <v>-11200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,36 +1493,39 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-322300</v>
+        <v>-49500</v>
       </c>
       <c r="E27" s="3">
-        <v>-212200</v>
+        <v>-25100</v>
       </c>
       <c r="F27" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-118000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-44400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="J27" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
         <v>-11200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1538,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1583,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1628,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,29 +1718,32 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1692,36 +1763,39 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-322300</v>
+        <v>-49500</v>
       </c>
       <c r="E33" s="3">
-        <v>-212200</v>
+        <v>-25100</v>
       </c>
       <c r="F33" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-118000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-44400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="J33" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
         <v>-11200</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1808,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,36 +1853,39 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-322300</v>
+        <v>-49500</v>
       </c>
       <c r="E35" s="3">
-        <v>-212200</v>
+        <v>-25100</v>
       </c>
       <c r="F35" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-118000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-44400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="J35" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
         <v>-11200</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,41 +1898,44 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
-        <v>44926</v>
-      </c>
-      <c r="G38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44196</v>
-      </c>
-      <c r="I38" s="2">
-        <v>43830</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="G38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1948,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,35 +1989,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>219900</v>
-      </c>
-      <c r="E41" s="3">
-        <v>185100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>340400</v>
-      </c>
-      <c r="G41" s="3">
-        <v>320400</v>
-      </c>
-      <c r="H41" s="3">
-        <v>321500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>94600</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>3100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,26 +2031,29 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1281600</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>410300</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>270300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>85100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1973,8 +2064,8 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -1982,41 +2073,44 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>28200</v>
-      </c>
-      <c r="E43" s="3">
-        <v>8600</v>
+        <v>100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3">
-        <v>3900</v>
-      </c>
-      <c r="G43" s="3">
-        <v>900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I43" s="3">
         <v>800</v>
       </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2027,9 +2121,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2057,8 +2154,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2069,14 +2166,17 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>1200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2111,36 +2211,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1542300</v>
+        <v>2800</v>
       </c>
       <c r="E46" s="3">
-        <v>611300</v>
+        <v>500</v>
       </c>
       <c r="F46" s="3">
-        <v>622900</v>
-      </c>
-      <c r="G46" s="3">
-        <v>411100</v>
-      </c>
-      <c r="H46" s="3">
-        <v>331700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>95700</v>
-      </c>
-      <c r="J46" s="3">
+        <v>900</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3">
         <v>3200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,9 +2256,12 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2183,8 +2289,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2195,36 +2301,39 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>18300</v>
+        <v>5500</v>
       </c>
       <c r="E48" s="3">
-        <v>16700</v>
+        <v>6700</v>
       </c>
       <c r="F48" s="3">
-        <v>15000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>15600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>600</v>
-      </c>
-      <c r="J48" s="3">
+        <v>9400</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3">
         <v>700</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,9 +2346,12 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2252,23 +2364,23 @@
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2279,9 +2391,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,35 +2481,38 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>3300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2405,9 +2526,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,36 +2571,39 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1563900</v>
+        <v>8400</v>
       </c>
       <c r="E54" s="3">
-        <v>628600</v>
+        <v>7200</v>
       </c>
       <c r="F54" s="3">
-        <v>638800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>427600</v>
-      </c>
-      <c r="H54" s="3">
-        <v>333900</v>
-      </c>
-      <c r="I54" s="3">
-        <v>96900</v>
-      </c>
-      <c r="J54" s="3">
+        <v>10300</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3">
         <v>4000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2616,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,35 +2657,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8500</v>
+        <v>4400</v>
       </c>
       <c r="E57" s="3">
-        <v>8800</v>
+        <v>500</v>
       </c>
       <c r="F57" s="3">
-        <v>4600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>7700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J57" s="3">
+        <v>500</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,36 +2699,39 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,29 +2744,32 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E59" s="3">
         <v>21000</v>
       </c>
-      <c r="E59" s="3">
-        <v>28400</v>
-      </c>
       <c r="F59" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3800</v>
+        <v>28200</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2651,36 +2789,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>98000</v>
+        <v>41800</v>
       </c>
       <c r="E60" s="3">
-        <v>80700</v>
+        <v>26800</v>
       </c>
       <c r="F60" s="3">
-        <v>51900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>29700</v>
-      </c>
-      <c r="H60" s="3">
-        <v>14600</v>
-      </c>
-      <c r="I60" s="3">
-        <v>10200</v>
-      </c>
-      <c r="J60" s="3">
+        <v>33800</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>4600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,36 +2834,39 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>3000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>7600</v>
       </c>
-      <c r="G61" s="3">
-        <v>10000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>900</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,17 +2879,20 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>600</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2756,15 +2903,15 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2924,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,36 +3059,39 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>138900</v>
+        <v>71100</v>
       </c>
       <c r="E66" s="3">
-        <v>127800</v>
+        <v>68300</v>
       </c>
       <c r="F66" s="3">
-        <v>60700</v>
-      </c>
-      <c r="G66" s="3">
-        <v>46200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>27700</v>
-      </c>
-      <c r="I66" s="3">
-        <v>27500</v>
-      </c>
-      <c r="J66" s="3">
+        <v>80900</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>12400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3104,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3213,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3069,14 +3238,14 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>134700</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>32700</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3089,9 +3258,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,36 +3303,39 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-893100</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-570800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-358500</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-184500</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-66500</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-22200</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>-41600</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3348,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,36 +3483,39 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1425000</v>
+        <v>-62700</v>
       </c>
       <c r="E76" s="3">
-        <v>500800</v>
+        <v>-61100</v>
       </c>
       <c r="F76" s="3">
-        <v>578100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>381400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>306200</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-65400</v>
-      </c>
-      <c r="J76" s="3">
+        <v>-70600</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K76" s="3">
         <v>-41100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3528,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,41 +3573,44 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
-        <v>44926</v>
-      </c>
-      <c r="G80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44196</v>
-      </c>
-      <c r="I80" s="2">
-        <v>43830</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="G80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,36 +3623,39 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-322300</v>
+        <v>-49500</v>
       </c>
       <c r="E81" s="3">
-        <v>-212200</v>
+        <v>-25100</v>
       </c>
       <c r="F81" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-118000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-44400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="J81" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
         <v>-11200</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3668,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,35 +3690,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2800</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>2100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
-      </c>
-      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
-        <v>300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>400</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3732,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,36 +3957,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300900</v>
+        <v>-41100</v>
       </c>
       <c r="E89" s="3">
-        <v>-119100</v>
+        <v>-22600</v>
       </c>
       <c r="F89" s="3">
-        <v>-136300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-94800</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-37100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J89" s="3">
+        <v>56400</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-9700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4002,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,34 +4024,35 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-7100</v>
+        <v>-1400</v>
       </c>
       <c r="E91" s="3">
-        <v>-4200</v>
+        <v>-300</v>
       </c>
       <c r="F91" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
@@ -3844,9 +4066,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,35 +4156,38 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-854200</v>
+        <v>-1400</v>
       </c>
       <c r="E94" s="3">
-        <v>-130100</v>
+        <v>-300</v>
       </c>
       <c r="F94" s="3">
-        <v>-190000</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-82500</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
@@ -3970,9 +4201,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4223,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4265,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,36 +4400,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1192400</v>
+        <v>42600</v>
       </c>
       <c r="E100" s="3">
-        <v>93900</v>
+        <v>22800</v>
       </c>
       <c r="F100" s="3">
-        <v>346200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>176300</v>
-      </c>
-      <c r="H100" s="3">
-        <v>272000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>89200</v>
-      </c>
-      <c r="J100" s="3">
+        <v>-56100</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>5100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,9 +4445,12 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4228,8 +4478,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4240,38 +4490,41 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>37300</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-155300</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>19900</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>227100</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>91500</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-4600</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4282,7 +4535,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
